--- a/Colaboradores_2.4/Colaboradores/Base_historica_Colaboradores.xlsx
+++ b/Colaboradores_2.4/Colaboradores/Base_historica_Colaboradores.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\954108\Desktop\codigos_py\Presentaciones\IPN_Colaboradores\Colaboradores\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70173B73-309A-4F1A-A472-5C77334E406D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Periodo</t>
   </si>
@@ -31,14 +37,74 @@
     <t>Detractores</t>
   </si>
   <si>
-    <t>2Q´26</t>
+    <t>1Q´21</t>
+  </si>
+  <si>
+    <t>2Q´21</t>
+  </si>
+  <si>
+    <t>3Q´21</t>
+  </si>
+  <si>
+    <t>4Q´21</t>
+  </si>
+  <si>
+    <t>1Q´22</t>
+  </si>
+  <si>
+    <t>2Q´22</t>
+  </si>
+  <si>
+    <t>3Q´22</t>
+  </si>
+  <si>
+    <t>4Q´22</t>
+  </si>
+  <si>
+    <t>1Q´23</t>
+  </si>
+  <si>
+    <t>2Q´23</t>
+  </si>
+  <si>
+    <t>3Q´23</t>
+  </si>
+  <si>
+    <t>4Q´23</t>
+  </si>
+  <si>
+    <t>1Q´24</t>
+  </si>
+  <si>
+    <t>2Q´24</t>
+  </si>
+  <si>
+    <t>3Q´24</t>
+  </si>
+  <si>
+    <t>4Q´24</t>
+  </si>
+  <si>
+    <t>1Q´25</t>
+  </si>
+  <si>
+    <t>2Q´25</t>
+  </si>
+  <si>
+    <t>3Q´25</t>
+  </si>
+  <si>
+    <t>4Q´25</t>
+  </si>
+  <si>
+    <t>1Q´26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,13 +141,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -119,7 +193,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -153,6 +227,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -187,9 +262,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -362,11 +438,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -383,21 +459,361 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.7024179034403609</v>
+        <v>0.62</v>
       </c>
       <c r="C2">
-        <v>0.7651216776650408</v>
+        <v>0.71899999999999997</v>
       </c>
       <c r="D2">
-        <v>0.1721745481102794</v>
+        <v>0.182</v>
       </c>
       <c r="E2">
-        <v>0.06270377422467983</v>
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="C3">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="D3">
+        <v>0.15</v>
+      </c>
+      <c r="E3">
+        <v>0.14499999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="C4">
+        <v>0.77</v>
+      </c>
+      <c r="D4">
+        <v>0.15</v>
+      </c>
+      <c r="E4">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="C5">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="D5">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>0.745</v>
+      </c>
+      <c r="C6">
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="D6">
+        <v>0.128</v>
+      </c>
+      <c r="E6">
+        <v>6.4000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="C7">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="D7">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E7">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="C8">
+        <v>0.8</v>
+      </c>
+      <c r="D8">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="E8">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="C9">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="D9">
+        <v>0.125</v>
+      </c>
+      <c r="E9">
+        <v>8.8999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>0.73399999999999999</v>
+      </c>
+      <c r="C10">
+        <v>0.80100000000000005</v>
+      </c>
+      <c r="D10">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="E10">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="C11">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="D11">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="E11">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="C12">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="D12">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="E12">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="C13">
+        <v>0.78400000000000003</v>
+      </c>
+      <c r="D13">
+        <v>0.155</v>
+      </c>
+      <c r="E13">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="C14">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="D14">
+        <v>0.158</v>
+      </c>
+      <c r="E14">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="C15">
+        <v>0.78</v>
+      </c>
+      <c r="D15">
+        <v>0.155</v>
+      </c>
+      <c r="E15">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="C16">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="D16">
+        <v>0.156</v>
+      </c>
+      <c r="E16">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="C17">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="D17">
+        <v>0.156</v>
+      </c>
+      <c r="E17">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="C18">
+        <v>0.76400000000000001</v>
+      </c>
+      <c r="D18">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="E18">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="C19">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="D19">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="E19">
+        <v>7.3999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="C20">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="D20">
+        <v>0.17</v>
+      </c>
+      <c r="E20">
+        <v>7.0999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="C21">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="D21">
+        <v>0.17</v>
+      </c>
+      <c r="E21">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22">
+        <v>0.70199999999999996</v>
+      </c>
+      <c r="C22">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="D22">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="E22">
+        <v>6.3E-2</v>
       </c>
     </row>
   </sheetData>
